--- a/output/pdf_financials_xlsx/CAM.xlsx
+++ b/output/pdf_financials_xlsx/CAM.xlsx
@@ -2206,13 +2206,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>-2.548229</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-2.187979</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>-1.470033</v>
       </c>
     </row>
     <row r="93">
@@ -3710,7 +3710,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4164,7 +4168,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAM.xlsx
+++ b/output/pdf_financials_xlsx/CAM.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.06449199999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.112538</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.05191</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.031628</v>
       </c>
     </row>
     <row r="13">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.755857</v>
+        <v>-1.820349</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.391814</v>
+        <v>-4.504352</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.46888</v>
+        <v>-5.52079</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.714605</v>
+        <v>-3.746233</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.749583</v>
+        <v>-1.814075</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.384978</v>
+        <v>-4.497516</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.464416</v>
+        <v>-5.516326</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.714047</v>
+        <v>-3.745675</v>
       </c>
     </row>
     <row r="30">
@@ -3960,7 +3960,11 @@
           <t>Reclamation deposit (Note 9)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.031</v>
       </c>
@@ -5808,7 +5812,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>-0.031</v>
       </c>
@@ -6532,7 +6540,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAM.xlsx
+++ b/output/pdf_financials_xlsx/CAM.xlsx
@@ -547,13 +547,13 @@
         <v>0.074472</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.170357</v>
+        <v>0.184357</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.073668</v>
+        <v>0.101668</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.06890499999999999</v>
+        <v>0.099077</v>
       </c>
     </row>
     <row r="8">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008312999999999999</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008312999999999999</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.142185</v>
+        <v>0.133872</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-3.507967</v>
@@ -5670,7 +5670,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>-0.008312999999999999</v>
       </c>
@@ -6000,7 +6004,11 @@
           <t>Directors’ fees (Note 12) $</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7672,7 +7680,11 @@
           <t>Directors’ fees (Note 14) $</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -8988,7 +9000,11 @@
           <t>Directors’ fees (Note 14)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
